--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12458"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22580" windowHeight="11270"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,66 +19,123 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+  <x:si>
+    <x:t>float[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰</x:t>
+  </x:si>
   <x:si>
     <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
   </x:si>
   <x:si>
+    <x:t>기본체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_slim_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_pigme_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
+    <x:t>도그는 도그다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalAtkMultiple</x:t>
   </x:si>
   <x:si>
     <x:t>몬스터 설명 (도감용)</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_slim_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_pigme_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>몬스터 표기용 Icon</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+    <x:t>기본공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_bear_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.5,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillAtkMultipleList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 공격 스킬 배율</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -179,16 +236,16 @@
   <x:borders count="3">
     <x:border>
       <x:left>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:left>
       <x:right>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:right>
       <x:top>
         <x:color auto="1"/>
       </x:top>
       <x:bottom>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -226,8 +283,8 @@
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="17">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
@@ -880,109 +937,162 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:O35"/>
+  <x:sheetPr codeName="Sheet1"/>
+  <x:dimension ref="A1:S35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.453125" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="50.7265625" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="20.26953125" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="30.54296875" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="26.54296875" style="3" customWidth="1"/>
-    <x:col min="7" max="16384" width="12.54296875" style="3"/>
+    <x:col min="4" max="5" width="20.26953125" style="3" customWidth="1"/>
+    <x:col min="6" max="6" width="25.53515625" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="7" max="7" width="54.4453125" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="20.26953125" style="3" customWidth="1"/>
+    <x:col min="9" max="9" width="30.54296875" style="3" customWidth="1"/>
+    <x:col min="10" max="10" width="26.54296875" style="3" customWidth="1"/>
+    <x:col min="11" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:6" ht="13.19999999999999928946">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F2" s="1"/>
-    </x:row>
-    <x:row r="3" spans="1:6" s="13" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J2" s="1"/>
+    </x:row>
+    <x:row r="3" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C3" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J3" s="15"/>
+    </x:row>
+    <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
+      <x:c r="A4" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D4" s="4">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E4" s="4">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F4" s="4">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C3" s="12" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
+      <x:c r="G4" s="4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F3" s="15"/>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D4" s="5"/>
-      <x:c r="E4" s="5"/>
-      <x:c r="F4" s="16"/>
-      <x:c r="G4" s="5"/>
-      <x:c r="H4" s="5"/>
-      <x:c r="I4" s="5"/>
-      <x:c r="J4" s="5"/>
+      <x:c r="H4" s="5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I4" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J4" s="16"/>
       <x:c r="K4" s="5"/>
       <x:c r="L4" s="5"/>
       <x:c r="M4" s="5"/>
       <x:c r="N4" s="5"/>
       <x:c r="O4" s="5"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P4" s="5"/>
+      <x:c r="Q4" s="5"/>
+      <x:c r="R4" s="5"/>
+      <x:c r="S4" s="5"/>
+    </x:row>
+    <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="5"/>
-      <x:c r="E5" s="5"/>
-      <x:c r="F5" s="5"/>
-      <x:c r="G5" s="5"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D5" s="6"/>
+      <x:c r="E5" s="6"/>
+      <x:c r="F5" s="6"/>
+      <x:c r="G5" s="6"/>
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5"/>
@@ -991,21 +1101,25 @@
       <x:c r="M5" s="5"/>
       <x:c r="N5" s="5"/>
       <x:c r="O5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P5" s="5"/>
+      <x:c r="Q5" s="5"/>
+      <x:c r="R5" s="5"/>
+      <x:c r="S5" s="5"/>
+    </x:row>
+    <x:row r="6" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="5"/>
-      <x:c r="E6" s="5"/>
-      <x:c r="F6" s="5"/>
-      <x:c r="G6" s="5"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D6" s="6"/>
+      <x:c r="E6" s="6"/>
+      <x:c r="F6" s="6"/>
+      <x:c r="G6" s="6"/>
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
@@ -1014,32 +1128,58 @@
       <x:c r="M6" s="5"/>
       <x:c r="N6" s="5"/>
       <x:c r="O6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="4"/>
-      <x:c r="B7" s="4"/>
-      <x:c r="C7" s="4"/>
-      <x:c r="D7" s="5"/>
-      <x:c r="E7" s="5"/>
-      <x:c r="F7" s="5"/>
-      <x:c r="G7" s="5"/>
-      <x:c r="H7" s="5"/>
-      <x:c r="I7" s="5"/>
+      <x:c r="P6" s="5"/>
+      <x:c r="Q6" s="5"/>
+      <x:c r="R6" s="5"/>
+      <x:c r="S6" s="5"/>
+    </x:row>
+    <x:row r="7" spans="1:19" ht="15.75" customHeight="1">
+      <x:c r="A7" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D7" s="4">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E7" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F7" s="4">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="G7" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5"/>
       <x:c r="L7" s="5"/>
       <x:c r="M7" s="5"/>
       <x:c r="N7" s="5"/>
       <x:c r="O7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P7" s="5"/>
+      <x:c r="Q7" s="5"/>
+      <x:c r="R7" s="5"/>
+      <x:c r="S7" s="5"/>
+    </x:row>
+    <x:row r="8" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A8" s="7"/>
       <x:c r="B8" s="7"/>
       <x:c r="C8" s="7"/>
-      <x:c r="D8" s="5"/>
-      <x:c r="E8" s="5"/>
-      <x:c r="F8" s="5"/>
-      <x:c r="G8" s="5"/>
+      <x:c r="D8" s="7"/>
+      <x:c r="E8" s="7"/>
+      <x:c r="F8" s="7"/>
+      <x:c r="G8" s="7"/>
       <x:c r="H8" s="5"/>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="5"/>
@@ -1048,15 +1188,19 @@
       <x:c r="M8" s="5"/>
       <x:c r="N8" s="5"/>
       <x:c r="O8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P8" s="5"/>
+      <x:c r="Q8" s="5"/>
+      <x:c r="R8" s="5"/>
+      <x:c r="S8" s="5"/>
+    </x:row>
+    <x:row r="9" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A9" s="7"/>
       <x:c r="B9" s="7"/>
       <x:c r="C9" s="7"/>
-      <x:c r="D9" s="5"/>
-      <x:c r="E9" s="5"/>
-      <x:c r="F9" s="5"/>
-      <x:c r="G9" s="5"/>
+      <x:c r="D9" s="7"/>
+      <x:c r="E9" s="7"/>
+      <x:c r="F9" s="7"/>
+      <x:c r="G9" s="7"/>
       <x:c r="H9" s="5"/>
       <x:c r="I9" s="5"/>
       <x:c r="J9" s="5"/>
@@ -1065,15 +1209,19 @@
       <x:c r="M9" s="5"/>
       <x:c r="N9" s="5"/>
       <x:c r="O9" s="5"/>
-    </x:row>
-    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P9" s="5"/>
+      <x:c r="Q9" s="5"/>
+      <x:c r="R9" s="5"/>
+      <x:c r="S9" s="5"/>
+    </x:row>
+    <x:row r="10" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1"/>
       <x:c r="C10" s="1"/>
-      <x:c r="D10" s="5"/>
-      <x:c r="E10" s="5"/>
-      <x:c r="F10" s="5"/>
-      <x:c r="G10" s="5"/>
+      <x:c r="D10" s="1"/>
+      <x:c r="E10" s="1"/>
+      <x:c r="F10" s="1"/>
+      <x:c r="G10" s="1"/>
       <x:c r="H10" s="5"/>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5"/>
@@ -1082,15 +1230,19 @@
       <x:c r="M10" s="5"/>
       <x:c r="N10" s="5"/>
       <x:c r="O10" s="5"/>
-    </x:row>
-    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P10" s="5"/>
+      <x:c r="Q10" s="5"/>
+      <x:c r="R10" s="5"/>
+      <x:c r="S10" s="5"/>
+    </x:row>
+    <x:row r="11" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
       <x:c r="C11" s="1"/>
-      <x:c r="D11" s="5"/>
-      <x:c r="E11" s="5"/>
-      <x:c r="F11" s="5"/>
-      <x:c r="G11" s="5"/>
+      <x:c r="D11" s="1"/>
+      <x:c r="E11" s="1"/>
+      <x:c r="F11" s="1"/>
+      <x:c r="G11" s="1"/>
       <x:c r="H11" s="5"/>
       <x:c r="I11" s="5"/>
       <x:c r="J11" s="5"/>
@@ -1099,15 +1251,19 @@
       <x:c r="M11" s="5"/>
       <x:c r="N11" s="5"/>
       <x:c r="O11" s="5"/>
-    </x:row>
-    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P11" s="5"/>
+      <x:c r="Q11" s="5"/>
+      <x:c r="R11" s="5"/>
+      <x:c r="S11" s="5"/>
+    </x:row>
+    <x:row r="12" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A12" s="7"/>
       <x:c r="B12" s="7"/>
       <x:c r="C12" s="7"/>
-      <x:c r="D12" s="5"/>
-      <x:c r="E12" s="5"/>
-      <x:c r="F12" s="5"/>
-      <x:c r="G12" s="5"/>
+      <x:c r="D12" s="7"/>
+      <x:c r="E12" s="7"/>
+      <x:c r="F12" s="7"/>
+      <x:c r="G12" s="7"/>
       <x:c r="H12" s="5"/>
       <x:c r="I12" s="5"/>
       <x:c r="J12" s="5"/>
@@ -1116,15 +1272,19 @@
       <x:c r="M12" s="5"/>
       <x:c r="N12" s="5"/>
       <x:c r="O12" s="5"/>
-    </x:row>
-    <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P12" s="5"/>
+      <x:c r="Q12" s="5"/>
+      <x:c r="R12" s="5"/>
+      <x:c r="S12" s="5"/>
+    </x:row>
+    <x:row r="13" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A13" s="4"/>
       <x:c r="B13" s="4"/>
       <x:c r="C13" s="4"/>
-      <x:c r="D13" s="5"/>
-      <x:c r="E13" s="5"/>
-      <x:c r="F13" s="5"/>
-      <x:c r="G13" s="5"/>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
       <x:c r="H13" s="5"/>
       <x:c r="I13" s="5"/>
       <x:c r="J13" s="5"/>
@@ -1133,15 +1293,19 @@
       <x:c r="M13" s="5"/>
       <x:c r="N13" s="5"/>
       <x:c r="O13" s="5"/>
-    </x:row>
-    <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P13" s="5"/>
+      <x:c r="Q13" s="5"/>
+      <x:c r="R13" s="5"/>
+      <x:c r="S13" s="5"/>
+    </x:row>
+    <x:row r="14" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
       <x:c r="C14" s="1"/>
-      <x:c r="D14" s="5"/>
-      <x:c r="E14" s="5"/>
-      <x:c r="F14" s="5"/>
-      <x:c r="G14" s="5"/>
+      <x:c r="D14" s="1"/>
+      <x:c r="E14" s="1"/>
+      <x:c r="F14" s="1"/>
+      <x:c r="G14" s="1"/>
       <x:c r="H14" s="5"/>
       <x:c r="I14" s="5"/>
       <x:c r="J14" s="5"/>
@@ -1150,15 +1314,19 @@
       <x:c r="M14" s="5"/>
       <x:c r="N14" s="5"/>
       <x:c r="O14" s="5"/>
-    </x:row>
-    <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P14" s="5"/>
+      <x:c r="Q14" s="5"/>
+      <x:c r="R14" s="5"/>
+      <x:c r="S14" s="5"/>
+    </x:row>
+    <x:row r="15" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
       <x:c r="C15" s="1"/>
-      <x:c r="D15" s="5"/>
-      <x:c r="E15" s="5"/>
-      <x:c r="F15" s="5"/>
-      <x:c r="G15" s="5"/>
+      <x:c r="D15" s="1"/>
+      <x:c r="E15" s="1"/>
+      <x:c r="F15" s="1"/>
+      <x:c r="G15" s="1"/>
       <x:c r="H15" s="5"/>
       <x:c r="I15" s="5"/>
       <x:c r="J15" s="5"/>
@@ -1167,112 +1335,196 @@
       <x:c r="M15" s="5"/>
       <x:c r="N15" s="5"/>
       <x:c r="O15" s="5"/>
-    </x:row>
-    <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="P15" s="5"/>
+      <x:c r="Q15" s="5"/>
+      <x:c r="R15" s="5"/>
+      <x:c r="S15" s="5"/>
+    </x:row>
+    <x:row r="16" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A16" s="8"/>
       <x:c r="B16" s="8"/>
       <x:c r="C16" s="8"/>
-    </x:row>
-    <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D16" s="8"/>
+      <x:c r="E16" s="8"/>
+      <x:c r="F16" s="8"/>
+      <x:c r="G16" s="8"/>
+    </x:row>
+    <x:row r="17" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A17" s="9"/>
       <x:c r="B17" s="9"/>
       <x:c r="C17" s="9"/>
-    </x:row>
-    <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D17" s="8"/>
+      <x:c r="E17" s="8"/>
+      <x:c r="F17" s="8"/>
+      <x:c r="G17" s="8"/>
+    </x:row>
+    <x:row r="18" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A18" s="9"/>
       <x:c r="B18" s="9"/>
       <x:c r="C18" s="9"/>
-    </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D18" s="8"/>
+      <x:c r="E18" s="8"/>
+      <x:c r="F18" s="8"/>
+      <x:c r="G18" s="8"/>
+    </x:row>
+    <x:row r="19" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A19" s="9"/>
       <x:c r="B19" s="9"/>
       <x:c r="C19" s="9"/>
-      <x:c r="D19" s="5"/>
-      <x:c r="E19" s="5"/>
-    </x:row>
-    <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D19" s="8"/>
+      <x:c r="E19" s="8"/>
+      <x:c r="F19" s="8"/>
+      <x:c r="G19" s="8"/>
+      <x:c r="H19" s="5"/>
+      <x:c r="I19" s="5"/>
+    </x:row>
+    <x:row r="20" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A20" s="9"/>
       <x:c r="B20" s="9"/>
       <x:c r="C20" s="9"/>
-    </x:row>
-    <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D20" s="8"/>
+      <x:c r="E20" s="8"/>
+      <x:c r="F20" s="8"/>
+      <x:c r="G20" s="8"/>
+    </x:row>
+    <x:row r="21" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A21" s="9"/>
       <x:c r="B21" s="9"/>
       <x:c r="C21" s="9"/>
-    </x:row>
-    <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D21" s="8"/>
+      <x:c r="E21" s="8"/>
+      <x:c r="F21" s="8"/>
+      <x:c r="G21" s="8"/>
+    </x:row>
+    <x:row r="22" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A22" s="9"/>
       <x:c r="B22" s="9"/>
       <x:c r="C22" s="9"/>
-    </x:row>
-    <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D22" s="8"/>
+      <x:c r="E22" s="8"/>
+      <x:c r="F22" s="8"/>
+      <x:c r="G22" s="8"/>
+    </x:row>
+    <x:row r="23" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A23" s="9"/>
       <x:c r="B23" s="9"/>
       <x:c r="C23" s="9"/>
-    </x:row>
-    <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D23" s="8"/>
+      <x:c r="E23" s="8"/>
+      <x:c r="F23" s="8"/>
+      <x:c r="G23" s="8"/>
+    </x:row>
+    <x:row r="24" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A24" s="9"/>
       <x:c r="B24" s="9"/>
       <x:c r="C24" s="9"/>
-    </x:row>
-    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D24" s="8"/>
+      <x:c r="E24" s="8"/>
+      <x:c r="F24" s="8"/>
+      <x:c r="G24" s="8"/>
+    </x:row>
+    <x:row r="25" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A25" s="9"/>
       <x:c r="B25" s="9"/>
       <x:c r="C25" s="9"/>
-      <x:c r="E25" s="5"/>
-    </x:row>
-    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D25" s="8"/>
+      <x:c r="E25" s="8"/>
+      <x:c r="F25" s="8"/>
+      <x:c r="G25" s="8"/>
+      <x:c r="I25" s="5"/>
+    </x:row>
+    <x:row r="26" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A26" s="10"/>
       <x:c r="B26" s="10"/>
       <x:c r="C26" s="10"/>
-      <x:c r="E26" s="5"/>
-    </x:row>
-    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D26" s="10"/>
+      <x:c r="E26" s="10"/>
+      <x:c r="F26" s="10"/>
+      <x:c r="G26" s="10"/>
+      <x:c r="I26" s="5"/>
+    </x:row>
+    <x:row r="27" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A27" s="10"/>
       <x:c r="B27" s="10"/>
       <x:c r="C27" s="10"/>
-      <x:c r="E27" s="5"/>
-    </x:row>
-    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="D27" s="10"/>
+      <x:c r="E27" s="10"/>
+      <x:c r="F27" s="10"/>
+      <x:c r="G27" s="10"/>
+      <x:c r="I27" s="5"/>
+    </x:row>
+    <x:row r="28" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A28" s="10"/>
       <x:c r="B28" s="10"/>
       <x:c r="C28" s="10"/>
-      <x:c r="E28" s="5"/>
-    </x:row>
-    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D28" s="10"/>
+      <x:c r="E28" s="10"/>
+      <x:c r="F28" s="10"/>
+      <x:c r="G28" s="10"/>
+      <x:c r="I28" s="5"/>
+    </x:row>
+    <x:row r="29" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A29" s="10"/>
       <x:c r="B29" s="10"/>
       <x:c r="C29" s="10"/>
-    </x:row>
-    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D29" s="10"/>
+      <x:c r="E29" s="10"/>
+      <x:c r="F29" s="10"/>
+      <x:c r="G29" s="10"/>
+    </x:row>
+    <x:row r="30" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A30" s="10"/>
       <x:c r="B30" s="10"/>
       <x:c r="C30" s="10"/>
-    </x:row>
-    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D30" s="10"/>
+      <x:c r="E30" s="10"/>
+      <x:c r="F30" s="10"/>
+      <x:c r="G30" s="10"/>
+    </x:row>
+    <x:row r="31" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A31" s="10"/>
       <x:c r="B31" s="10"/>
       <x:c r="C31" s="10"/>
-    </x:row>
-    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D31" s="10"/>
+      <x:c r="E31" s="10"/>
+      <x:c r="F31" s="10"/>
+      <x:c r="G31" s="10"/>
+    </x:row>
+    <x:row r="32" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A32" s="11"/>
       <x:c r="B32" s="11"/>
       <x:c r="C32" s="11"/>
-    </x:row>
-    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D32" s="11"/>
+      <x:c r="E32" s="11"/>
+      <x:c r="F32" s="11"/>
+      <x:c r="G32" s="11"/>
+    </x:row>
+    <x:row r="33" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A33" s="11"/>
       <x:c r="B33" s="11"/>
       <x:c r="C33" s="11"/>
-    </x:row>
-    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D33" s="11"/>
+      <x:c r="E33" s="11"/>
+      <x:c r="F33" s="11"/>
+      <x:c r="G33" s="11"/>
+    </x:row>
+    <x:row r="34" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A34" s="11"/>
       <x:c r="B34" s="11"/>
       <x:c r="C34" s="11"/>
-    </x:row>
-    <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="D34" s="11"/>
+      <x:c r="E34" s="11"/>
+      <x:c r="F34" s="11"/>
+      <x:c r="G34" s="11"/>
+    </x:row>
+    <x:row r="35" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A35" s="11"/>
       <x:c r="B35" s="11"/>
       <x:c r="C35" s="11"/>
+      <x:c r="D35" s="11"/>
+      <x:c r="E35" s="11"/>
+      <x:c r="F35" s="11"/>
+      <x:c r="G35" s="11"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>
@@ -2240,7 +2492,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -21,121 +21,121 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <x:si>
+    <x:t>SkillAtkMultipleList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_bear_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 공격 스킬 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_slim_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_pigme_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 표기용 Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그는 도그다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.5,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseHp</x:t>
+  </x:si>
+  <x:si>
     <x:t>float[]</x:t>
   </x:si>
   <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Slime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>기본체력</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_slim_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_pigme_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그</x:t>
-  </x:si>
-  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>슬라이무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
+    <x:t>NormalAtkMultiple</x:t>
   </x:si>
   <x:si>
     <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
   </x:si>
   <x:si>
     <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NormalAtkMultiple</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 표기용 Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_bear_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DObject/Monster_Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DObject/Monster_Slime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.5,5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillAtkMultipleList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 공격 스킬 배율</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -955,100 +955,100 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="J2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E3" s="12" t="s">
-        <x:v>34</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F3" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G3" s="12" t="s">
-        <x:v>37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I3" s="14" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J3" s="15"/>
     </x:row>
     <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D4" s="4">
         <x:v>500</x:v>
@@ -1063,10 +1063,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I4" s="5" t="s">
         <x:v>2</x:v>
-      </x:c>
-      <x:c r="I4" s="5" t="s">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="J4" s="16"/>
       <x:c r="K4" s="5"/>
@@ -1081,13 +1081,13 @@
     </x:row>
     <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D5" s="6"/>
       <x:c r="E5" s="6"/>
@@ -1108,13 +1108,13 @@
     </x:row>
     <x:row r="6" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="6"/>
       <x:c r="E6" s="6"/>
@@ -1135,13 +1135,13 @@
     </x:row>
     <x:row r="7" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D7" s="4">
         <x:v>1000</x:v>
@@ -1153,13 +1153,13 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J7" s="5"/>
       <x:c r="K7" s="5"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="16332" windowHeight="6744"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,123 +19,138 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+  <x:si>
+    <x:t>Unique</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalAtkMultiple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
   <x:si>
     <x:t>SkillAtkMultipleList</x:t>
   </x:si>
   <x:si>
+    <x:t>2DObject/Monster_Slime</x:t>
+  </x:si>
+  <x:si>
     <x:t>2DObject/Monster_Bear</x:t>
   </x:si>
   <x:si>
-    <x:t>2DObject/Monster_Slime</x:t>
+    <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 공격 스킬 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_bear_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_pigme_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_slim_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.5,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그는 도그다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰</x:t>
   </x:si>
   <x:si>
     <x:t>피그미</x:t>
   </x:si>
   <x:si>
-    <x:t>곰</x:t>
-  </x:si>
-  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>도그</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_bear_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 공격 스킬 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_slim_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_pigme_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
+    <x:t>몬스터 설명 (도감용)</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Slime</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
+    <x:t>Icon/Icon_Bear</x:t>
   </x:si>
   <x:si>
     <x:t>몬스터 표기용 Icon</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.5,5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본체력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NormalAtkMultiple</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+    <x:t>몬스터타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MonsterType</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -233,7 +248,7 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="3">
+  <x:borders count="2">
     <x:border>
       <x:left>
         <x:color auto="1"/>
@@ -262,27 +277,13 @@
         <x:color auto="1"/>
       </x:bottom>
     </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="ff000000"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="ff000000"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="ff000000"/>
-      </x:top>
-      <x:bottom style="thin">
-        <x:color rgb="ff000000"/>
-      </x:bottom>
-    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -330,9 +331,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -953,102 +951,109 @@
     <x:col min="11" max="16384" width="12.54296875" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:9" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J1" s="3" t="s">
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="J2" s="1"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>6</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E3" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F3" s="12" t="s">
-        <x:v>36</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="12" t="s">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I3" s="14" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J3" s="15"/>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J3" s="15" t="s">
+        <x:v>43</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="4">
         <x:v>500</x:v>
@@ -1063,12 +1068,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J4" s="16"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J4" s="5" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="K4" s="5"/>
       <x:c r="L4" s="5"/>
       <x:c r="M4" s="5"/>
@@ -1081,13 +1088,13 @@
     </x:row>
     <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D5" s="6"/>
       <x:c r="E5" s="6"/>
@@ -1095,7 +1102,9 @@
       <x:c r="G5" s="6"/>
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
-      <x:c r="J5" s="5"/>
+      <x:c r="J5" s="5" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="K5" s="5"/>
       <x:c r="L5" s="5"/>
       <x:c r="M5" s="5"/>
@@ -1108,13 +1117,13 @@
     </x:row>
     <x:row r="6" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="6"/>
       <x:c r="E6" s="6"/>
@@ -1122,7 +1131,9 @@
       <x:c r="G6" s="6"/>
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
-      <x:c r="J6" s="5"/>
+      <x:c r="J6" s="5" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="K6" s="5"/>
       <x:c r="L6" s="5"/>
       <x:c r="M6" s="5"/>
@@ -1135,13 +1146,13 @@
     </x:row>
     <x:row r="7" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="4">
         <x:v>1000</x:v>
@@ -1153,15 +1164,17 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J7" s="5"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J7" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="K7" s="5"/>
       <x:c r="L7" s="5"/>
       <x:c r="M7" s="5"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -21,136 +21,136 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
   <x:si>
+    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 표기용 Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 공격 스킬 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_slim_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_bear_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_pigme_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MonsterType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미</x:t>
+  </x:si>
+  <x:si>
     <x:t>Unique</x:t>
   </x:si>
   <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그는 도그다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.5,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
     <x:t>NormalAtkMultiple</x:t>
   </x:si>
   <x:si>
-    <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+    <x:t>2DObject/Monster_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Bear</x:t>
   </x:si>
   <x:si>
     <x:t>SkillAtkMultipleList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DObject/Monster_Slime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DObject/Monster_Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 공격 스킬 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_bear_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_pigme_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_slim_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.5,5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본체력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Slime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 표기용 Icon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MonsterType</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -953,110 +953,110 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="J1" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E3" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F3" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G3" s="12" t="s">
-        <x:v>4</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H3" s="14" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J3" s="15" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="I3" s="14" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J3" s="15" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D4" s="4">
-        <x:v>500</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E4" s="4">
         <x:v>20</x:v>
@@ -1068,13 +1068,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J4" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K4" s="5"/>
       <x:c r="L4" s="5"/>
@@ -1088,10 +1088,10 @@
     </x:row>
     <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
         <x:v>28</x:v>
@@ -1103,7 +1103,7 @@
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
       <x:c r="J5" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="K5" s="5"/>
       <x:c r="L5" s="5"/>
@@ -1120,10 +1120,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="6"/>
       <x:c r="E6" s="6"/>
@@ -1132,7 +1132,7 @@
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="K6" s="5"/>
       <x:c r="L6" s="5"/>
@@ -1149,13 +1149,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D7" s="4">
-        <x:v>1000</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="E7" s="4">
         <x:v>100</x:v>
@@ -1164,16 +1164,16 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="J7" s="5" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="5" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I7" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="J7" s="5" t="s">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="K7" s="5"/>
       <x:c r="L7" s="5"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="44">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <x:si>
     <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
   </x:si>
@@ -27,123 +27,114 @@
     <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
   </x:si>
   <x:si>
+    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalAtkMultiple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그는 도그다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.5,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_pigme_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MonsterType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_slim_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 공격 스킬 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_bear_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Bear</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Slime</x:t>
   </x:si>
   <x:si>
     <x:t>몬스터 표기용 Icon</x:t>
   </x:si>
   <x:si>
-    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 공격 스킬 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_slim_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_bear_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_pigme_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MonsterType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unique</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본체력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.5,5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NormalAtkMultiple</x:t>
-  </x:si>
-  <x:si>
     <x:t>2DObject/Monster_Slime</x:t>
   </x:si>
   <x:si>
@@ -151,6 +142,9 @@
   </x:si>
   <x:si>
     <x:t>SkillAtkMultipleList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elite</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -953,107 +947,107 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>39</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="J1" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>18</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="J3" s="15" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F3" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I3" s="14" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J3" s="15" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D4" s="4">
         <x:v>100</x:v>
@@ -1068,14 +1062,12 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="J4" s="5" t="s">
-        <x:v>33</x:v>
-      </x:c>
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
       <x:c r="L4" s="5"/>
       <x:c r="M4" s="5"/>
@@ -1088,13 +1080,13 @@
     </x:row>
     <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="6"/>
       <x:c r="E5" s="6"/>
@@ -1102,9 +1094,7 @@
       <x:c r="G5" s="6"/>
       <x:c r="H5" s="5"/>
       <x:c r="I5" s="5"/>
-      <x:c r="J5" s="5" t="s">
-        <x:v>33</x:v>
-      </x:c>
+      <x:c r="J5" s="5"/>
       <x:c r="K5" s="5"/>
       <x:c r="L5" s="5"/>
       <x:c r="M5" s="5"/>
@@ -1117,10 +1107,10 @@
     </x:row>
     <x:row r="6" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
         <x:v>0</x:v>
@@ -1131,9 +1121,7 @@
       <x:c r="G6" s="6"/>
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
-      <x:c r="J6" s="5" t="s">
-        <x:v>23</x:v>
-      </x:c>
+      <x:c r="J6" s="5"/>
       <x:c r="K6" s="5"/>
       <x:c r="L6" s="5"/>
       <x:c r="M6" s="5"/>
@@ -1146,13 +1134,13 @@
     </x:row>
     <x:row r="7" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="4">
         <x:v>300</x:v>
@@ -1164,16 +1152,16 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J7" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="K7" s="5"/>
       <x:c r="L7" s="5"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="16332" windowHeight="6744"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -21,130 +21,130 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <x:si>
+    <x:t>몬스터 표기용 Icon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Slime</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.5,5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그는 도그다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NormalAtkMultiple</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+  </x:si>
+  <x:si>
     <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
   </x:si>
   <x:si>
     <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
   </x:si>
   <x:si>
-    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NormalAtkMultiple</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본체력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.5,5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseAtk</x:t>
+    <x:t>mob_slim_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MonsterType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
   </x:si>
   <x:si>
     <x:t>mob_pigme_1</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MonsterType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_slim_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
+    <x:t>mob_bear_1</x:t>
   </x:si>
   <x:si>
     <x:t>일반 공격 스킬 배율</x:t>
   </x:si>
   <x:si>
-    <x:t>mob_bear_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Slime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몬스터 표기용 Icon</x:t>
+    <x:t>SkillAtkMultipleList</x:t>
   </x:si>
   <x:si>
     <x:t>2DObject/Monster_Slime</x:t>
   </x:si>
   <x:si>
     <x:t>2DObject/Monster_Bear</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillAtkMultipleList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Elite</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -947,29 +947,29 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="J1" s="3" t="s">
         <x:v>16</x:v>
@@ -977,77 +977,77 @@
     </x:row>
     <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D3" s="12" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F3" s="12" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="I3" s="14" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="J3" s="15" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D4" s="4">
         <x:v>100</x:v>
@@ -1062,10 +1062,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
@@ -1080,13 +1080,13 @@
     </x:row>
     <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="6"/>
       <x:c r="E5" s="6"/>
@@ -1107,13 +1107,13 @@
     </x:row>
     <x:row r="6" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="6"/>
       <x:c r="E6" s="6"/>
@@ -1134,13 +1134,13 @@
     </x:row>
     <x:row r="7" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D7" s="4">
         <x:v>300</x:v>
@@ -1152,16 +1152,16 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="J7" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K7" s="5"/>
       <x:c r="L7" s="5"/>

--- a/JsonConverter/ExcelFiles/DNMonster.xlsx
+++ b/JsonConverter/ExcelFiles/DNMonster.xlsx
@@ -19,75 +19,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
+  <x:si>
+    <x:t>기본몹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>곰</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_normal_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트몹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간색 몹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초록색 몹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_normal_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_bear_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MonsterType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_pigme_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_dog_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 공격 스킬 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_slim_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터 설명 (도감용)</x:t>
+  </x:si>
   <x:si>
     <x:t>몬스터 표기용 Icon</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터 설명 (도감용)</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Bear</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Slime</x:t>
   </x:si>
   <x:si>
-    <x:t>곰</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그</x:t>
+    <x:t>BaseHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몬스터타입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도그는 도그다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본체력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseAtk</x:t>
   </x:si>
   <x:si>
     <x:t>Name</x:t>
   </x:si>
   <x:si>
-    <x:t>BaseHp</x:t>
+    <x:t>1.5,5</x:t>
   </x:si>
   <x:si>
     <x:t>슬라이무</x:t>
   </x:si>
   <x:si>
-    <x:t>BaseAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Elite</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본체력</x:t>
-  </x:si>
-  <x:si>
     <x:t>기본공격력</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터타입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.5,5</x:t>
-  </x:si>
-  <x:si>
     <x:t>float[]</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도그는 도그다</x:t>
+    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
   </x:si>
   <x:si>
     <x:t>곰이다. 곰은 사람을 찢는다.</x:t>
@@ -96,55 +156,67 @@
     <x:t>NormalAtkMultiple</x:t>
   </x:si>
   <x:si>
-    <x:t>몬스터를 우선 프리팹으로 구현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슬라이무는 공격을 받을 때마다 딸기맛, 초코맛, 바닐라맛으로 변한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피그미는 충돌하면 사라진다. 간헐적으로 금화가 터져나온다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스킬 공격의 배율 리스트(나중에 스킬 데이터로 빠질 수 있다)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_slim_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MonsterType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_dog_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_pigme_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_bear_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 공격 스킬 배율</x:t>
+    <x:t>2DObject/Monster_Normal_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Normal_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Bear</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Slime</x:t>
   </x:si>
   <x:si>
     <x:t>SkillAtkMultipleList</x:t>
   </x:si>
   <x:si>
-    <x:t>2DObject/Monster_Slime</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2DObject/Monster_Bear</x:t>
+    <x:t>mob_event_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_green_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_red_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>초록몹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간몹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본몹2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_EventMob</x:t>
+  </x:si>
+  <x:si>
+    <x:t>좀 더 큰 기본몹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트 발생시 나오는 몹</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_NormalMob_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_NormalMob_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Green</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Event</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2DObject/Monster_Red</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_GreenMob</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_RedMob</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -947,107 +1019,107 @@
   <x:sheetData>
     <x:row r="1" spans="1:10" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="J1" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:10" s="13" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="12" t="s">
-        <x:v>9</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3" s="12" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E3" s="12" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F3" s="12" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J3" s="15" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="F3" s="12" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="H3" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="I3" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="J3" s="15" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D4" s="4">
         <x:v>100</x:v>
@@ -1062,10 +1134,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I4" s="5" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J4" s="5"/>
       <x:c r="K4" s="5"/>
@@ -1080,13 +1152,13 @@
     </x:row>
     <x:row r="5" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D5" s="6"/>
       <x:c r="E5" s="6"/>
@@ -1107,13 +1179,13 @@
     </x:row>
     <x:row r="6" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A6" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D6" s="6"/>
       <x:c r="E6" s="6"/>
@@ -1134,13 +1206,13 @@
     </x:row>
     <x:row r="7" spans="1:19" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D7" s="4">
         <x:v>300</x:v>
@@ -1152,16 +1224,16 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H7" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I7" s="5" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="J7" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K7" s="5"/>
       <x:c r="L7" s="5"/>
@@ -1174,15 +1246,29 @@
       <x:c r="S7" s="5"/>
     </x:row>
     <x:row r="8" spans="1:19" ht="15.75" customHeight="1">
-      <x:c r="A8" s="7"/>
-      <x:c r="B8" s="7"/>
-      <x:c r="C8" s="7"/>
-      <x:c r="D8" s="7"/>
-      <x:c r="E8" s="7"/>
+      <x:c r="A8" s="7" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="7">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E8" s="7">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="F8" s="7"/>
       <x:c r="G8" s="7"/>
-      <x:c r="H8" s="5"/>
-      <x:c r="I8" s="5"/>
+      <x:c r="H8" s="5" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I8" s="5" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="J8" s="5"/>
       <x:c r="K8" s="5"/>
       <x:c r="L8" s="5"/>
@@ -1195,15 +1281,29 @@
       <x:c r="S8" s="5"/>
     </x:row>
     <x:row r="9" spans="1:19" ht="15.75" customHeight="1">
-      <x:c r="A9" s="7"/>
-      <x:c r="B9" s="7"/>
-      <x:c r="C9" s="7"/>
-      <x:c r="D9" s="7"/>
-      <x:c r="E9" s="7"/>
+      <x:c r="A9" s="7" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D9" s="7">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="E9" s="7">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="F9" s="7"/>
       <x:c r="G9" s="7"/>
-      <x:c r="H9" s="5"/>
-      <x:c r="I9" s="5"/>
+      <x:c r="H9" s="5" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I9" s="5" t="s">
+        <x:v>46</x:v>
+      </x:c>
       <x:c r="J9" s="5"/>
       <x:c r="K9" s="5"/>
       <x:c r="L9" s="5"/>
@@ -1216,15 +1316,29 @@
       <x:c r="S9" s="5"/>
     </x:row>
     <x:row r="10" spans="1:19" ht="15.75" customHeight="1">
-      <x:c r="A10" s="1"/>
-      <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
+      <x:c r="A10" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D10" s="1">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="E10" s="1">
+        <x:v>80</x:v>
+      </x:c>
       <x:c r="F10" s="1"/>
       <x:c r="G10" s="1"/>
-      <x:c r="H10" s="5"/>
-      <x:c r="I10" s="5"/>
+      <x:c r="H10" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I10" s="5" t="s">
+        <x:v>61</x:v>
+      </x:c>
       <x:c r="J10" s="5"/>
       <x:c r="K10" s="5"/>
       <x:c r="L10" s="5"/>
@@ -1237,16 +1351,32 @@
       <x:c r="S10" s="5"/>
     </x:row>
     <x:row r="11" spans="1:19" ht="15.75" customHeight="1">
-      <x:c r="A11" s="1"/>
-      <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
+      <x:c r="A11" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D11" s="1">
+        <x:v>3000</x:v>
+      </x:c>
+      <x:c r="E11" s="1">
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="F11" s="1"/>
       <x:c r="G11" s="1"/>
-      <x:c r="H11" s="5"/>
-      <x:c r="I11" s="5"/>
-      <x:c r="J11" s="5"/>
+      <x:c r="H11" s="5" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I11" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="J11" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="K11" s="5"/>
       <x:c r="L11" s="5"/>
       <x:c r="M11" s="5"/>
@@ -1258,16 +1388,32 @@
       <x:c r="S11" s="5"/>
     </x:row>
     <x:row r="12" spans="1:19" ht="15.75" customHeight="1">
-      <x:c r="A12" s="7"/>
-      <x:c r="B12" s="7"/>
-      <x:c r="C12" s="7"/>
-      <x:c r="D12" s="7"/>
-      <x:c r="E12" s="7"/>
+      <x:c r="A12" s="7" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B12" s="7" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C12" s="7" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D12" s="7">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E12" s="7">
+        <x:v>300</x:v>
+      </x:c>
       <x:c r="F12" s="7"/>
       <x:c r="G12" s="7"/>
-      <x:c r="H12" s="5"/>
-      <x:c r="I12" s="5"/>
-      <x:c r="J12" s="5"/>
+      <x:c r="H12" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I12" s="5" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J12" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="K12" s="5"/>
       <x:c r="L12" s="5"/>
       <x:c r="M12" s="5"/>
